--- a/ER_sem_outliers.xlsx
+++ b/ER_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>23.92833333333333</v>
+        <v>24.9928</v>
       </c>
       <c r="D2">
-        <v>25.947</v>
+        <v>27.49966666666667</v>
       </c>
       <c r="E2">
-        <v>24.35</v>
+        <v>25.7095</v>
       </c>
       <c r="F2">
-        <v>24.597</v>
-      </c>
-      <c r="G2">
-        <v>25.321</v>
+        <v>24.20475</v>
       </c>
       <c r="H2">
-        <v>23.992</v>
+        <v>7.908200000000001</v>
+      </c>
+      <c r="I2">
+        <v>6.515000000000001</v>
       </c>
       <c r="J2">
-        <v>24.4755</v>
+        <v>4.526</v>
+      </c>
+      <c r="K2">
+        <v>6.1392</v>
       </c>
       <c r="L2">
-        <v>25.293</v>
+        <v>3.67975</v>
+      </c>
+      <c r="M2">
+        <v>5.1112</v>
       </c>
     </row>
     <row r="3">
@@ -476,27 +482,6 @@
       <c r="F3">
         <v>19.11733333333333</v>
       </c>
-      <c r="G3">
-        <v>22.87516666666667</v>
-      </c>
-      <c r="H3">
-        <v>20.4932</v>
-      </c>
-      <c r="I3">
-        <v>22.6276</v>
-      </c>
-      <c r="J3">
-        <v>25.4558</v>
-      </c>
-      <c r="K3">
-        <v>21.041</v>
-      </c>
-      <c r="L3">
-        <v>15.857</v>
-      </c>
-      <c r="M3">
-        <v>20.7036</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -508,34 +493,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>26.2234</v>
+        <v>27.017</v>
       </c>
       <c r="D4">
-        <v>25.968</v>
+        <v>7.036199999999999</v>
       </c>
       <c r="E4">
-        <v>27.55933333333333</v>
+        <v>5.0256</v>
       </c>
       <c r="F4">
-        <v>25.91166666666667</v>
+        <v>3.379</v>
       </c>
       <c r="G4">
-        <v>25.7755</v>
+        <v>3.156166666666667</v>
       </c>
       <c r="H4">
-        <v>25.548</v>
+        <v>2.4455</v>
       </c>
       <c r="I4">
-        <v>24.23433333333334</v>
+        <v>2.356166666666667</v>
       </c>
       <c r="J4">
-        <v>24.05133333333333</v>
+        <v>2.106666666666667</v>
       </c>
       <c r="K4">
-        <v>25.033</v>
+        <v>2.928</v>
       </c>
       <c r="L4">
-        <v>20.012</v>
+        <v>2.104333333333333</v>
+      </c>
+      <c r="M4">
+        <v>3.133666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +536,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>25.61733333333333</v>
+        <v>24.003</v>
       </c>
       <c r="D5">
-        <v>24.876</v>
+        <v>10.844</v>
       </c>
       <c r="E5">
-        <v>25.1722</v>
+        <v>7.5685</v>
       </c>
       <c r="F5">
-        <v>24.5835</v>
+        <v>4.3758</v>
       </c>
       <c r="G5">
-        <v>24.05525</v>
+        <v>4.866</v>
       </c>
       <c r="H5">
-        <v>24.634</v>
+        <v>3.5144</v>
       </c>
       <c r="I5">
-        <v>25.0165</v>
+        <v>2.8344</v>
       </c>
       <c r="J5">
-        <v>24.949</v>
+        <v>2.838</v>
+      </c>
+      <c r="K5">
+        <v>6.006</v>
       </c>
       <c r="L5">
-        <v>25.686</v>
+        <v>4.230333333333333</v>
       </c>
       <c r="M5">
-        <v>24.88633333333333</v>
+        <v>4.548999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -674,34 +665,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>26.2504</v>
+        <v>27.176</v>
+      </c>
+      <c r="D8">
+        <v>22.6795</v>
       </c>
       <c r="E8">
-        <v>25.361</v>
+        <v>21.773</v>
       </c>
       <c r="F8">
-        <v>27.149</v>
-      </c>
-      <c r="G8">
-        <v>26.75166666666667</v>
-      </c>
-      <c r="H8">
-        <v>23.462</v>
-      </c>
-      <c r="I8">
-        <v>26.0568</v>
-      </c>
-      <c r="J8">
-        <v>27.6305</v>
-      </c>
-      <c r="K8">
-        <v>25.988</v>
-      </c>
-      <c r="L8">
-        <v>25.672</v>
-      </c>
-      <c r="M8">
-        <v>26.48575</v>
+        <v>24.53633333333334</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +687,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>26.54225</v>
+        <v>24.276</v>
       </c>
       <c r="D9">
-        <v>25.8955</v>
+        <v>10.82425</v>
+      </c>
+      <c r="E9">
+        <v>6.242500000000001</v>
       </c>
       <c r="F9">
-        <v>25.6462</v>
+        <v>3.4235</v>
       </c>
       <c r="G9">
-        <v>25.3295</v>
+        <v>8.2074</v>
       </c>
       <c r="H9">
-        <v>25.97616666666667</v>
+        <v>7.787</v>
       </c>
       <c r="I9">
-        <v>25.9324</v>
+        <v>3.791166666666667</v>
       </c>
       <c r="J9">
-        <v>26.163</v>
+        <v>1.8835</v>
       </c>
       <c r="K9">
-        <v>26.6715</v>
+        <v>4.258833333333333</v>
       </c>
       <c r="L9">
-        <v>27.2846</v>
+        <v>7.3036</v>
       </c>
       <c r="M9">
-        <v>26.262</v>
+        <v>2.7726</v>
       </c>
     </row>
     <row r="10">
@@ -883,31 +859,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>27.13633333333333</v>
+        <v>23.5246</v>
+      </c>
+      <c r="D13">
+        <v>10.35375</v>
       </c>
       <c r="E13">
-        <v>27.144</v>
+        <v>5.8352</v>
+      </c>
+      <c r="F13">
+        <v>4.369166666666667</v>
       </c>
       <c r="G13">
-        <v>25.086</v>
+        <v>4.462000000000001</v>
       </c>
       <c r="H13">
-        <v>21.72</v>
+        <v>5.25</v>
       </c>
       <c r="I13">
-        <v>20.277</v>
+        <v>4.1552</v>
       </c>
       <c r="J13">
-        <v>21.7245</v>
+        <v>2.639666666666666</v>
       </c>
       <c r="K13">
-        <v>21.284</v>
+        <v>2.982</v>
       </c>
       <c r="L13">
-        <v>25.048</v>
+        <v>5.7544</v>
       </c>
       <c r="M13">
-        <v>23.02</v>
+        <v>2.307333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -963,37 +945,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>24.4828</v>
+        <v>20.4745</v>
       </c>
       <c r="D15">
-        <v>24.514</v>
+        <v>4.3156</v>
       </c>
       <c r="E15">
-        <v>25.39433333333334</v>
+        <v>3.4124</v>
       </c>
       <c r="F15">
-        <v>25.424</v>
+        <v>4.596166666666666</v>
       </c>
       <c r="G15">
-        <v>26.346</v>
+        <v>6.408799999999999</v>
       </c>
       <c r="H15">
-        <v>25.9626</v>
+        <v>4.565</v>
       </c>
       <c r="I15">
-        <v>25.5894</v>
+        <v>2.02675</v>
       </c>
       <c r="J15">
-        <v>26.0374</v>
+        <v>2.615</v>
       </c>
       <c r="K15">
-        <v>25.952</v>
+        <v>3.3408</v>
       </c>
       <c r="L15">
-        <v>24.69133333333333</v>
+        <v>4.656499999999999</v>
       </c>
       <c r="M15">
-        <v>24.12133333333334</v>
+        <v>4.5378</v>
       </c>
     </row>
     <row r="16">
@@ -1048,6 +1030,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>23.83625</v>
+      </c>
+      <c r="D17">
+        <v>19.7128</v>
+      </c>
+      <c r="E17">
+        <v>19.3968</v>
+      </c>
+      <c r="F17">
+        <v>9.4015</v>
+      </c>
+      <c r="G17">
+        <v>6.535</v>
+      </c>
+      <c r="H17">
+        <v>6.137</v>
+      </c>
+      <c r="I17">
+        <v>5.056166666666667</v>
+      </c>
+      <c r="J17">
+        <v>3.27675</v>
+      </c>
+      <c r="K17">
+        <v>2.863</v>
+      </c>
+      <c r="L17">
+        <v>4.030333333333334</v>
+      </c>
+      <c r="M17">
+        <v>3.3254</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1058,6 +1073,9 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C18">
+        <v>17.81166666666667</v>
+      </c>
       <c r="D18">
         <v>4.002166666666667</v>
       </c>
@@ -1107,18 +1125,6 @@
       <c r="F19">
         <v>20.92633333333333</v>
       </c>
-      <c r="G19">
-        <v>21.5215</v>
-      </c>
-      <c r="H19">
-        <v>23.2558</v>
-      </c>
-      <c r="I19">
-        <v>15.8484</v>
-      </c>
-      <c r="J19">
-        <v>10.91066666666667</v>
-      </c>
       <c r="K19">
         <v>6.1226</v>
       </c>
@@ -1611,9 +1617,6 @@
       <c r="D31">
         <v>17.53833333333333</v>
       </c>
-      <c r="E31">
-        <v>17.20533333333333</v>
-      </c>
       <c r="H31">
         <v>5.384166666666666</v>
       </c>
@@ -1648,9 +1651,6 @@
       <c r="D32">
         <v>20.9596</v>
       </c>
-      <c r="E32">
-        <v>15.75983333333333</v>
-      </c>
       <c r="F32">
         <v>3.102</v>
       </c>
@@ -1981,10 +1981,34 @@
         </is>
       </c>
       <c r="C40">
-        <v>25.2575</v>
+        <v>9.216666666666667</v>
       </c>
       <c r="D40">
-        <v>24.5118</v>
+        <v>5.592</v>
+      </c>
+      <c r="E40">
+        <v>5.110666666666666</v>
+      </c>
+      <c r="F40">
+        <v>3.9918</v>
+      </c>
+      <c r="G40">
+        <v>5.442666666666667</v>
+      </c>
+      <c r="I40">
+        <v>5.885333333333333</v>
+      </c>
+      <c r="J40">
+        <v>3.571</v>
+      </c>
+      <c r="K40">
+        <v>5.492999999999999</v>
+      </c>
+      <c r="L40">
+        <v>4.265333333333333</v>
+      </c>
+      <c r="M40">
+        <v>6.247666666666666</v>
       </c>
     </row>
     <row r="41">
